--- a/03-analysis/CR-04A_指标计算结果.xlsx
+++ b/03-analysis/CR-04A_指标计算结果.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原始周度宽表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="质量等级来源长表" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excel公式审计示例" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公式说明" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公式审计_可运行样例" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19776,14 +19778,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19821,21 +19823,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>欧洲航线</t>
+          <t>SCFI综合指数</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>以指标结果_数值源中该航线26周value计算</t>
+          <t>最近26周该航线数值的95分位</t>
         </is>
       </c>
       <c r="D2">
-        <f>PERCENTILE.INC(FILTER(指标结果_数值源!C:C,指标结果_数值源!B:B="欧洲航线"),0.95)</f>
+        <f>PERCENTILE.INC('原始周度宽表'!B$2:B$27,0.95)</f>
         <v/>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
@@ -19847,21 +19849,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>欧洲航线</t>
+          <t>SCFI综合指数</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>本周/上周-1</t>
+          <t>本周相对上周变化百分比</t>
         </is>
       </c>
       <c r="D3">
-        <f>IFERROR((C3/C2-1),"")</f>
+        <f>('原始周度宽表'!B$27/'原始周度宽表'!B$26-1)*100</f>
         <v/>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
@@ -19873,255 +19875,255 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欧洲航线</t>
+          <t>SCFI综合指数</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(本周值-均值)/标准差</t>
+          <t>本周值相对最近26周均值和样本标准差的标准化偏离</t>
         </is>
       </c>
       <c r="D4">
-        <f>IFERROR((C2-AVERAGE(C:C))/STDEV.P(C:C),"")</f>
+        <f>('原始周度宽表'!B$27-AVERAGE('原始周度宽表'!B$2:B$27))/STDEV.S('原始周度宽表'!B$2:B$27)</f>
         <v/>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P95分位</t>
+          <t>连续上涨周数</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>地中海航线</t>
+          <t>SCFI综合指数</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>以指标结果_数值源中该航线26周value计算</t>
+          <t>从最新周向前逐周检查，遇到非上涨即重置；样例最多回看5周</t>
         </is>
       </c>
       <c r="D5">
-        <f>PERCENTILE.INC(FILTER(指标结果_数值源!C:C,指标结果_数值源!B:B="地中海航线"),0.95)</f>
+        <f>IF('原始周度宽表'!B$27&lt;='原始周度宽表'!B$26,0,IF('原始周度宽表'!B$26&lt;='原始周度宽表'!B$25,1,IF('原始周度宽表'!B$25&lt;='原始周度宽表'!B$24,2,IF('原始周度宽表'!B$24&lt;='原始周度宽表'!B$23,3,IF('原始周度宽表'!B$23&lt;='原始周度宽表'!B$22,4,5)))))</f>
         <v/>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>周环比</t>
+          <t>P95分位</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>地中海航线</t>
+          <t>欧洲航线</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>本周/上周-1</t>
+          <t>最近26周该航线数值的95分位</t>
         </is>
       </c>
       <c r="D6">
-        <f>IFERROR((C3/C2-1),"")</f>
+        <f>PERCENTILE.INC('原始周度宽表'!D$2:D$27,0.95)</f>
         <v/>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Z分数</t>
+          <t>周环比</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>地中海航线</t>
+          <t>欧洲航线</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(本周值-均值)/标准差</t>
+          <t>本周相对上周变化百分比</t>
         </is>
       </c>
       <c r="D7">
-        <f>IFERROR((C2-AVERAGE(C:C))/STDEV.P(C:C),"")</f>
+        <f>('原始周度宽表'!D$27/'原始周度宽表'!D$26-1)*100</f>
         <v/>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P95分位</t>
+          <t>Z分数</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>美西航线</t>
+          <t>欧洲航线</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>以指标结果_数值源中该航线26周value计算</t>
+          <t>本周值相对最近26周均值和样本标准差的标准化偏离</t>
         </is>
       </c>
       <c r="D8">
-        <f>PERCENTILE.INC(FILTER(指标结果_数值源!C:C,指标结果_数值源!B:B="美西航线"),0.95)</f>
+        <f>('原始周度宽表'!D$27-AVERAGE('原始周度宽表'!D$2:D$27))/STDEV.S('原始周度宽表'!D$2:D$27)</f>
         <v/>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>周环比</t>
+          <t>连续上涨周数</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>美西航线</t>
+          <t>欧洲航线</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>本周/上周-1</t>
+          <t>从最新周向前逐周检查，遇到非上涨即重置；样例最多回看5周</t>
         </is>
       </c>
       <c r="D9">
-        <f>IFERROR((C3/C2-1),"")</f>
+        <f>IF('原始周度宽表'!D$27&lt;='原始周度宽表'!D$26,0,IF('原始周度宽表'!D$26&lt;='原始周度宽表'!D$25,1,IF('原始周度宽表'!D$25&lt;='原始周度宽表'!D$24,2,IF('原始周度宽表'!D$24&lt;='原始周度宽表'!D$23,3,IF('原始周度宽表'!D$23&lt;='原始周度宽表'!D$22,4,5)))))</f>
         <v/>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Z分数</t>
+          <t>P95分位</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>美西航线</t>
+          <t>地中海航线</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(本周值-均值)/标准差</t>
+          <t>最近26周该航线数值的95分位</t>
         </is>
       </c>
       <c r="D10">
-        <f>IFERROR((C2-AVERAGE(C:C))/STDEV.P(C:C),"")</f>
+        <f>PERCENTILE.INC('原始周度宽表'!C$2:C$27,0.95)</f>
         <v/>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P95分位</t>
+          <t>周环比</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>美东航线</t>
+          <t>地中海航线</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>以指标结果_数值源中该航线26周value计算</t>
+          <t>本周相对上周变化百分比</t>
         </is>
       </c>
       <c r="D11">
-        <f>PERCENTILE.INC(FILTER(指标结果_数值源!C:C,指标结果_数值源!B:B="美东航线"),0.95)</f>
+        <f>('原始周度宽表'!C$27/'原始周度宽表'!C$26-1)*100</f>
         <v/>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>周环比</t>
+          <t>Z分数</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>美东航线</t>
+          <t>地中海航线</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>本周/上周-1</t>
+          <t>本周值相对最近26周均值和样本标准差的标准化偏离</t>
         </is>
       </c>
       <c r="D12">
-        <f>IFERROR((C3/C2-1),"")</f>
+        <f>('原始周度宽表'!C$27-AVERAGE('原始周度宽表'!C$2:C$27))/STDEV.S('原始周度宽表'!C$2:C$27)</f>
         <v/>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Z分数</t>
+          <t>连续上涨周数</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>美东航线</t>
+          <t>地中海航线</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(本周值-均值)/标准差</t>
+          <t>从最新周向前逐周检查，遇到非上涨即重置；样例最多回看5周</t>
         </is>
       </c>
       <c r="D13">
-        <f>IFERROR((C2-AVERAGE(C:C))/STDEV.P(C:C),"")</f>
+        <f>IF('原始周度宽表'!C$27&lt;='原始周度宽表'!C$26,0,IF('原始周度宽表'!C$26&lt;='原始周度宽表'!C$25,1,IF('原始周度宽表'!C$25&lt;='原始周度宽表'!C$24,2,IF('原始周度宽表'!C$24&lt;='原始周度宽表'!C$23,3,IF('原始周度宽表'!C$23&lt;='原始周度宽表'!C$22,4,5)))))</f>
         <v/>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
@@ -20133,21 +20135,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SCFI综合指数</t>
+          <t>美西航线</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>以指标结果_数值源中该航线26周value计算</t>
+          <t>最近26周该航线数值的95分位</t>
         </is>
       </c>
       <c r="D14">
-        <f>PERCENTILE.INC(FILTER(指标结果_数值源!C:C,指标结果_数值源!B:B="SCFI综合指数"),0.95)</f>
+        <f>PERCENTILE.INC('原始周度宽表'!F$2:F$27,0.95)</f>
         <v/>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
@@ -20159,21 +20161,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SCFI综合指数</t>
+          <t>美西航线</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>本周/上周-1</t>
+          <t>本周相对上周变化百分比</t>
         </is>
       </c>
       <c r="D15">
-        <f>IFERROR((C3/C2-1),"")</f>
+        <f>('原始周度宽表'!F$27/'原始周度宽表'!F$26-1)*100</f>
         <v/>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>保留公式样例</t>
+          <t>可运行公式</t>
         </is>
       </c>
     </row>
@@ -20185,22 +20187,517 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>美西航线</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>本周值相对最近26周均值和样本标准差的标准化偏离</t>
+        </is>
+      </c>
+      <c r="D16">
+        <f>('原始周度宽表'!F$27-AVERAGE('原始周度宽表'!F$2:F$27))/STDEV.S('原始周度宽表'!F$2:F$27)</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>可运行公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>连续上涨周数</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>美西航线</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>从最新周向前逐周检查，遇到非上涨即重置；样例最多回看5周</t>
+        </is>
+      </c>
+      <c r="D17">
+        <f>IF('原始周度宽表'!F$27&lt;='原始周度宽表'!F$26,0,IF('原始周度宽表'!F$26&lt;='原始周度宽表'!F$25,1,IF('原始周度宽表'!F$25&lt;='原始周度宽表'!F$24,2,IF('原始周度宽表'!F$24&lt;='原始周度宽表'!F$23,3,IF('原始周度宽表'!F$23&lt;='原始周度宽表'!F$22,4,5)))))</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>可运行公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P95分位</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>美东航线</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>最近26周该航线数值的95分位</t>
+        </is>
+      </c>
+      <c r="D18">
+        <f>PERCENTILE.INC('原始周度宽表'!E$2:E$27,0.95)</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>可运行公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>周环比</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>美东航线</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>本周相对上周变化百分比</t>
+        </is>
+      </c>
+      <c r="D19">
+        <f>('原始周度宽表'!E$27/'原始周度宽表'!E$26-1)*100</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>可运行公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Z分数</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>美东航线</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>本周值相对最近26周均值和样本标准差的标准化偏离</t>
+        </is>
+      </c>
+      <c r="D20">
+        <f>('原始周度宽表'!E$27-AVERAGE('原始周度宽表'!E$2:E$27))/STDEV.S('原始周度宽表'!E$2:E$27)</f>
+        <v/>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>可运行公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>连续上涨周数</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>美东航线</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>从最新周向前逐周检查，遇到非上涨即重置；样例最多回看5周</t>
+        </is>
+      </c>
+      <c r="D21">
+        <f>IF('原始周度宽表'!E$27&lt;='原始周度宽表'!E$26,0,IF('原始周度宽表'!E$26&lt;='原始周度宽表'!E$25,1,IF('原始周度宽表'!E$25&lt;='原始周度宽表'!E$24,2,IF('原始周度宽表'!E$24&lt;='原始周度宽表'!E$23,3,IF('原始周度宽表'!E$23&lt;='原始周度宽表'!E$22,4,5)))))</f>
+        <v/>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>可运行公式</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>计算逻辑</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Excel公式原则</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P25/P50/P75/P85/P90/P95/P99</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>对同一航线最近26周value计算分位数</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PERCENTILE.INC(最近26周范围, 分位参数)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>用于判断历史相对位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>周环比</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>本周value/上周value-1</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>(本周单元格/上周单元格-1)*100</f>
+        <v/>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>首周为空</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Z分数</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(本周value-最近26周均值)/最近26周样本标准差</t>
+        </is>
+      </c>
+      <c r="C4">
+        <f>(本周值-AVERAGE(范围))/STDEV.S(范围)</f>
+        <v/>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>用于识别异常偏离</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>连续上涨周数</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>从最新周向前检查，遇到非上涨即重置</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>嵌套IF或辅助列递推</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>本审计样例采用嵌套IF，最多展示5周</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>预警标签</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>分位、周环比、Z分数、连续上涨组合打标</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TEXTJOIN + IF组合</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P85/P95、涨幅、Z≥2/3、连续上涨≥3/5周</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>航线</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>最新值</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>P95公式</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>周环比公式</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Z分数公式</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>连续上涨公式</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>预警标签公式</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>SCFI综合指数</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>(本周值-均值)/标准差</t>
-        </is>
-      </c>
-      <c r="D16">
-        <f>IFERROR((C2-AVERAGE(C:C))/STDEV.P(C:C),"")</f>
+      <c r="B2">
+        <f>'原始周度宽表'!B$27</f>
         <v/>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>保留公式样例</t>
-        </is>
+      <c r="C2">
+        <f>PERCENTILE.INC('原始周度宽表'!B$2:B$27,0.95)</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>('原始周度宽表'!B$27/'原始周度宽表'!B$26-1)*100</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>('原始周度宽表'!B$27-AVERAGE('原始周度宽表'!B$2:B$27))/STDEV.S('原始周度宽表'!B$2:B$27)</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>IF('原始周度宽表'!B$27&lt;='原始周度宽表'!B$26,0,IF('原始周度宽表'!B$26&lt;='原始周度宽表'!B$25,1,IF('原始周度宽表'!B$25&lt;='原始周度宽表'!B$24,2,IF('原始周度宽表'!B$24&lt;='原始周度宽表'!B$23,3,IF('原始周度宽表'!B$23&lt;='原始周度宽表'!B$22,4,5)))))</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>TEXTJOIN(";",TRUE,IF(B2&gt;=C2,"P95高位",""),IF(E2&gt;=2,"Z≥2异常",""),IF(F2&gt;=3,"连续上涨≥3周",""),IF(D2&lt;=-5,"周环比下跌≥5%",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>欧洲航线</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>'原始周度宽表'!D$27</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>PERCENTILE.INC('原始周度宽表'!D$2:D$27,0.95)</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>('原始周度宽表'!D$27/'原始周度宽表'!D$26-1)*100</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>('原始周度宽表'!D$27-AVERAGE('原始周度宽表'!D$2:D$27))/STDEV.S('原始周度宽表'!D$2:D$27)</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>IF('原始周度宽表'!D$27&lt;='原始周度宽表'!D$26,0,IF('原始周度宽表'!D$26&lt;='原始周度宽表'!D$25,1,IF('原始周度宽表'!D$25&lt;='原始周度宽表'!D$24,2,IF('原始周度宽表'!D$24&lt;='原始周度宽表'!D$23,3,IF('原始周度宽表'!D$23&lt;='原始周度宽表'!D$22,4,5)))))</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>TEXTJOIN(";",TRUE,IF(B3&gt;=C3,"P95高位",""),IF(E3&gt;=2,"Z≥2异常",""),IF(F3&gt;=3,"连续上涨≥3周",""),IF(D3&lt;=-5,"周环比下跌≥5%",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>地中海航线</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>'原始周度宽表'!C$27</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>PERCENTILE.INC('原始周度宽表'!C$2:C$27,0.95)</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>('原始周度宽表'!C$27/'原始周度宽表'!C$26-1)*100</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>('原始周度宽表'!C$27-AVERAGE('原始周度宽表'!C$2:C$27))/STDEV.S('原始周度宽表'!C$2:C$27)</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>IF('原始周度宽表'!C$27&lt;='原始周度宽表'!C$26,0,IF('原始周度宽表'!C$26&lt;='原始周度宽表'!C$25,1,IF('原始周度宽表'!C$25&lt;='原始周度宽表'!C$24,2,IF('原始周度宽表'!C$24&lt;='原始周度宽表'!C$23,3,IF('原始周度宽表'!C$23&lt;='原始周度宽表'!C$22,4,5)))))</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>TEXTJOIN(";",TRUE,IF(B4&gt;=C4,"P95高位",""),IF(E4&gt;=2,"Z≥2异常",""),IF(F4&gt;=3,"连续上涨≥3周",""),IF(D4&lt;=-5,"周环比下跌≥5%",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>美西航线</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>'原始周度宽表'!F$27</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>PERCENTILE.INC('原始周度宽表'!F$2:F$27,0.95)</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>('原始周度宽表'!F$27/'原始周度宽表'!F$26-1)*100</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>('原始周度宽表'!F$27-AVERAGE('原始周度宽表'!F$2:F$27))/STDEV.S('原始周度宽表'!F$2:F$27)</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>IF('原始周度宽表'!F$27&lt;='原始周度宽表'!F$26,0,IF('原始周度宽表'!F$26&lt;='原始周度宽表'!F$25,1,IF('原始周度宽表'!F$25&lt;='原始周度宽表'!F$24,2,IF('原始周度宽表'!F$24&lt;='原始周度宽表'!F$23,3,IF('原始周度宽表'!F$23&lt;='原始周度宽表'!F$22,4,5)))))</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>TEXTJOIN(";",TRUE,IF(B5&gt;=C5,"P95高位",""),IF(E5&gt;=2,"Z≥2异常",""),IF(F5&gt;=3,"连续上涨≥3周",""),IF(D5&lt;=-5,"周环比下跌≥5%",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>美东航线</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>'原始周度宽表'!E$27</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>PERCENTILE.INC('原始周度宽表'!E$2:E$27,0.95)</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>('原始周度宽表'!E$27/'原始周度宽表'!E$26-1)*100</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>('原始周度宽表'!E$27-AVERAGE('原始周度宽表'!E$2:E$27))/STDEV.S('原始周度宽表'!E$2:E$27)</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>IF('原始周度宽表'!E$27&lt;='原始周度宽表'!E$26,0,IF('原始周度宽表'!E$26&lt;='原始周度宽表'!E$25,1,IF('原始周度宽表'!E$25&lt;='原始周度宽表'!E$24,2,IF('原始周度宽表'!E$24&lt;='原始周度宽表'!E$23,3,IF('原始周度宽表'!E$23&lt;='原始周度宽表'!E$22,4,5)))))</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>TEXTJOIN(";",TRUE,IF(B6&gt;=C6,"P95高位",""),IF(E6&gt;=2,"Z≥2异常",""),IF(F6&gt;=3,"连续上涨≥3周",""),IF(D6&lt;=-5,"周环比下跌≥5%",""))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
